--- a/artfynd/A 55132-2024 artfynd.xlsx
+++ b/artfynd/A 55132-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106018674</v>
+        <v>106018677</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>5754</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559031.336728977</v>
+        <v>559196</v>
       </c>
       <c r="R2" t="n">
-        <v>6753373.412041497</v>
+        <v>6753351</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,27 +743,18 @@
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106018677</v>
+        <v>106018675</v>
       </c>
       <c r="B3" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5754</v>
+        <v>220075</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559196.4220921248</v>
+        <v>559086</v>
       </c>
       <c r="R3" t="n">
-        <v>6753350.856950791</v>
+        <v>6753507</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,28 +841,17 @@
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,15 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106018680</v>
+        <v>106018673</v>
       </c>
       <c r="B4" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559139.9564840945</v>
+        <v>558982</v>
       </c>
       <c r="R4" t="n">
-        <v>6753317.80581882</v>
+        <v>6753379</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,19 +938,9 @@
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,15 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106018673</v>
+        <v>106018674</v>
       </c>
       <c r="B5" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558982.0274075501</v>
+        <v>559031</v>
       </c>
       <c r="R5" t="n">
-        <v>6753378.918627017</v>
+        <v>6753374</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,19 +1035,9 @@
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,15 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106018678</v>
+        <v>106018680</v>
       </c>
       <c r="B6" t="n">
-        <v>86312</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>239221</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Papegojvaxskivling</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Herink</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559244</v>
+        <v>559140</v>
       </c>
       <c r="R6" t="n">
-        <v>6753342</v>
+        <v>6753318</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1143,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1224,6 +1158,95 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>106018678</v>
+      </c>
+      <c r="B7" t="n">
+        <v>89060</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>239221</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Gliophorus psittacinus var. psittacinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>N Båtpers, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>559245</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6753342</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Svartnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55132-2024 artfynd.xlsx
+++ b/artfynd/A 55132-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106018677</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106018675</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106018673</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106018674</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106018680</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1247,8 +1277,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106018678</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 55132-2024 artfynd.xlsx
+++ b/artfynd/A 55132-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1186,100 +1186,6 @@
       <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/106018680</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>106018678</v>
-      </c>
-      <c r="B7" t="n">
-        <v>89060</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>239221</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Gliophorus psittacinus var. psittacinus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>N Båtpers, Dlr</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>559245</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6753342</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Svartnäs</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Veronica Jägbrant</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Veronica Jägbrant</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/106018678</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1196,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55132-2024 artfynd.xlsx
+++ b/artfynd/A 55132-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106018677</v>
+        <v>106018678</v>
       </c>
       <c r="B2" t="n">
-        <v>91443</v>
+        <v>89207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5754</v>
+        <v>4393</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Papegojvaxing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Gliophorus psittacinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Schaeff.) Herink</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559196</v>
+        <v>559245</v>
       </c>
       <c r="R2" t="n">
-        <v>6753351</v>
+        <v>6753342</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,16 +777,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106018677</t>
+          <t>https://artportalen.se/Sighting/106018678</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106018675</v>
+        <v>106018677</v>
       </c>
       <c r="B3" t="n">
-        <v>101897</v>
+        <v>91443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,21 +794,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220075</v>
+        <v>5754</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chrysosplenium alternifolium</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559086</v>
+        <v>559196</v>
       </c>
       <c r="R3" t="n">
-        <v>6753507</v>
+        <v>6753351</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +862,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,33 +880,33 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106018675</t>
+          <t>https://artportalen.se/Sighting/106018677</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106018673</v>
+        <v>106018675</v>
       </c>
       <c r="B4" t="n">
-        <v>104628</v>
+        <v>101897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>220075</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -920,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558982</v>
+        <v>559086</v>
       </c>
       <c r="R4" t="n">
-        <v>6753379</v>
+        <v>6753507</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,13 +982,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106018673</t>
+          <t>https://artportalen.se/Sighting/106018675</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106018674</v>
+        <v>106018673</v>
       </c>
       <c r="B5" t="n">
         <v>104628</v>
@@ -1022,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559031</v>
+        <v>558982</v>
       </c>
       <c r="R5" t="n">
-        <v>6753374</v>
+        <v>6753379</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,13 +1084,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106018674</t>
+          <t>https://artportalen.se/Sighting/106018673</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106018680</v>
+        <v>106018674</v>
       </c>
       <c r="B6" t="n">
         <v>104628</v>
@@ -1124,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559140</v>
+        <v>559031</v>
       </c>
       <c r="R6" t="n">
-        <v>6753318</v>
+        <v>6753374</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,6 +1185,108 @@
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106018674</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>106018680</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>N Båtpers, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>559140</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6753318</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Svartnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/106018680</t>
         </is>
@@ -1196,6 +1299,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55132-2024 artfynd.xlsx
+++ b/artfynd/A 55132-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>106018678</v>
       </c>
       <c r="B2" t="n">
-        <v>89207</v>
+        <v>89213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55132-2024 artfynd.xlsx
+++ b/artfynd/A 55132-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>106018678</v>
       </c>
       <c r="B2" t="n">
-        <v>89213</v>
+        <v>89220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55132-2024 artfynd.xlsx
+++ b/artfynd/A 55132-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>106018678</v>
       </c>
       <c r="B2" t="n">
-        <v>89220</v>
+        <v>89221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55132-2024 artfynd.xlsx
+++ b/artfynd/A 55132-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>106018678</v>
       </c>
       <c r="B2" t="n">
-        <v>89221</v>
+        <v>89234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55132-2024 artfynd.xlsx
+++ b/artfynd/A 55132-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>106018678</v>
       </c>
       <c r="B2" t="n">
-        <v>89234</v>
+        <v>89235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
